--- a/output/roomself_excel/14668.xlsx
+++ b/output/roomself_excel/14668.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>84270</v>
+        <v>52954</v>
       </c>
       <c r="D2" t="n">
-        <v>2332</v>
+        <v>2364</v>
       </c>
       <c r="E2" t="n">
-        <v>359</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
-        <v>286</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>106156</v>
+        <v>211253</v>
       </c>
       <c r="D3" t="n">
-        <v>4012</v>
+        <v>4020</v>
       </c>
       <c r="E3" t="n">
-        <v>819</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>662</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>75174</v>
+        <v>84270</v>
       </c>
       <c r="D4" t="n">
-        <v>2276</v>
+        <v>2332</v>
       </c>
       <c r="E4" t="n">
-        <v>365</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>347614</v>
+        <v>75174</v>
       </c>
       <c r="D5" t="n">
-        <v>7564</v>
+        <v>2276</v>
       </c>
       <c r="E5" t="n">
-        <v>820</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>665</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>600</v>
+        <v>14750</v>
       </c>
       <c r="D6" t="n">
-        <v>200</v>
+        <v>972</v>
       </c>
       <c r="E6" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>19072</v>
+        <v>29600</v>
       </c>
       <c r="D7" t="n">
-        <v>1108</v>
+        <v>1400</v>
       </c>
       <c r="E7" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -602,10 +602,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14750</v>
+        <v>23476</v>
       </c>
       <c r="D8" t="n">
-        <v>972</v>
+        <v>1240</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>67475</v>
+        <v>83407</v>
       </c>
       <c r="D9" t="n">
-        <v>2144</v>
+        <v>3376</v>
       </c>
       <c r="E9" t="n">
-        <v>662</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1045</v>
+        <v>19072</v>
       </c>
       <c r="D10" t="n">
-        <v>296</v>
+        <v>1108</v>
       </c>
       <c r="E10" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>69353</v>
+        <v>40920</v>
       </c>
       <c r="D11" t="n">
-        <v>2136</v>
+        <v>1844</v>
       </c>
       <c r="E11" t="n">
-        <v>305</v>
+        <v>341</v>
       </c>
       <c r="F11" t="n">
-        <v>271</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29600</v>
+        <v>106156</v>
       </c>
       <c r="D12" t="n">
-        <v>1400</v>
+        <v>4012</v>
       </c>
       <c r="E12" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -712,16 +712,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>20502</v>
+        <v>600</v>
       </c>
       <c r="D13" t="n">
-        <v>1148</v>
+        <v>200</v>
       </c>
       <c r="E13" t="n">
-        <v>212</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -730,20 +730,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23476</v>
+        <v>67475</v>
       </c>
       <c r="D14" t="n">
-        <v>1240</v>
+        <v>2144</v>
       </c>
       <c r="E14" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -756,16 +756,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>121</v>
+        <v>1045</v>
       </c>
       <c r="D15" t="n">
-        <v>88</v>
+        <v>296</v>
       </c>
       <c r="E15" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -778,16 +778,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>589</v>
+        <v>69353</v>
       </c>
       <c r="D16" t="n">
-        <v>200</v>
+        <v>2136</v>
       </c>
       <c r="E16" t="n">
-        <v>198</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -796,20 +796,64 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>40920</v>
+        <v>20502</v>
       </c>
       <c r="D17" t="n">
-        <v>1844</v>
+        <v>1148</v>
       </c>
       <c r="E17" t="n">
-        <v>341</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>152</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>121</v>
+      </c>
+      <c r="D18" t="n">
+        <v>88</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>589</v>
+      </c>
+      <c r="D19" t="n">
+        <v>200</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/14668.xlsx
+++ b/output/roomself_excel/14668.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,12 +495,12 @@
       <c r="D2" t="n">
         <v>2364</v>
       </c>
-      <c r="E2" t="n">
-        <v>11</v>
-      </c>
-      <c r="F2" t="n">
-        <v>7</v>
-      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +517,12 @@
       <c r="D3" t="n">
         <v>4020</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +539,12 @@
       <c r="D4" t="n">
         <v>2332</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +561,12 @@
       <c r="D5" t="n">
         <v>2276</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +583,12 @@
       <c r="D6" t="n">
         <v>972</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +605,12 @@
       <c r="D7" t="n">
         <v>1400</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +627,12 @@
       <c r="D8" t="n">
         <v>1240</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +649,12 @@
       <c r="D9" t="n">
         <v>3376</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +671,12 @@
       <c r="D10" t="n">
         <v>1108</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,11 +693,27 @@
       <c r="D11" t="n">
         <v>1844</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>341</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>12</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>120</v>
+      </c>
+      <c r="J11" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="12">
@@ -695,12 +731,12 @@
       <c r="D12" t="n">
         <v>4012</v>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +753,12 @@
       <c r="D13" t="n">
         <v>200</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +775,12 @@
       <c r="D14" t="n">
         <v>2144</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +797,12 @@
       <c r="D15" t="n">
         <v>296</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +819,12 @@
       <c r="D16" t="n">
         <v>2136</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +841,12 @@
       <c r="D17" t="n">
         <v>1148</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +863,12 @@
       <c r="D18" t="n">
         <v>88</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +885,12 @@
       <c r="D19" t="n">
         <v>200</v>
       </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/14668.xlsx
+++ b/output/roomself_excel/14668.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,6 +477,26 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
         </is>
       </c>
     </row>
@@ -501,6 +521,10 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -523,6 +547,10 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -545,6 +573,10 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -567,6 +599,10 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -589,6 +625,10 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -611,6 +651,10 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -633,6 +677,10 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -655,6 +703,10 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -677,6 +729,10 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -714,6 +770,22 @@
       </c>
       <c r="J11" t="n">
         <v>13</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>91</v>
+      </c>
+      <c r="N11" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -737,6 +809,10 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -759,6 +835,10 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -781,6 +861,10 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -803,6 +887,10 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -825,6 +913,10 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -847,6 +939,10 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -869,6 +965,10 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -891,6 +991,10 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
